--- a/artfynd/A 55723-2022 artfynd.xlsx
+++ b/artfynd/A 55723-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55723-2022 artfynd.xlsx
+++ b/artfynd/A 55723-2022 artfynd.xlsx
@@ -1883,7 +1883,7 @@
         <v>131732483</v>
       </c>
       <c r="B12" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>131736514</v>
       </c>
       <c r="B13" t="n">
-        <v>78673</v>
+        <v>78675</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>131733026</v>
       </c>
       <c r="B14" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>131732490</v>
       </c>
       <c r="B15" t="n">
-        <v>91847</v>
+        <v>91850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>131733024</v>
       </c>
       <c r="B16" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>131736515</v>
       </c>
       <c r="B17" t="n">
-        <v>78673</v>
+        <v>78675</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>131733025</v>
       </c>
       <c r="B18" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>131735775</v>
       </c>
       <c r="B19" t="n">
-        <v>92477</v>
+        <v>92480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>131732385</v>
       </c>
       <c r="B20" t="n">
-        <v>96403</v>
+        <v>96406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>131737141</v>
       </c>
       <c r="B21" t="n">
-        <v>75405</v>
+        <v>75407</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 55723-2022 artfynd.xlsx
+++ b/artfynd/A 55723-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97309063</v>
+        <v>131733024</v>
       </c>
       <c r="B2" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3884</v>
+        <v>311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Torstorp Väst, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542504.6849128271</v>
+        <v>542504</v>
       </c>
       <c r="R2" t="n">
-        <v>6507008.474239124</v>
+        <v>6506958</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97309042</v>
+        <v>131733025</v>
       </c>
       <c r="B3" t="n">
-        <v>89940</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3884</v>
+        <v>311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Torstorp Väst, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542606.6712293181</v>
+        <v>542468</v>
       </c>
       <c r="R3" t="n">
-        <v>6507250.708601156</v>
+        <v>6506932</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97309056</v>
+        <v>131733026</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>83355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Mäselnleden Sydost, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542602.4439148868</v>
+        <v>542471</v>
       </c>
       <c r="R4" t="n">
-        <v>6507113.996262537</v>
+        <v>6507021</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +962,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97309065</v>
+        <v>131737141</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>75452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>1460</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Torstorp Väst, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542663.5890351037</v>
+        <v>542486</v>
       </c>
       <c r="R5" t="n">
-        <v>6506997.743800011</v>
+        <v>6506934</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,65 +1063,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97309055</v>
+        <v>131734436</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>2558</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Krushättemossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Ulota crispa s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Mäselnleden Sydost, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542614.1672576661</v>
+        <v>542603</v>
       </c>
       <c r="R6" t="n">
-        <v>6507041.892578379</v>
+        <v>6507108</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1140,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På hassel</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1165,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105911641</v>
+        <v>131732385</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,50 +1192,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Viggestorp Nord, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542571.1784522765</v>
+        <v>542607</v>
       </c>
       <c r="R7" t="n">
-        <v>6507021.67415525</v>
+        <v>6507006</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,22 +1246,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1348,27 +1266,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105908549</v>
+        <v>97309042</v>
       </c>
       <c r="B8" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,58 +1293,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>3884</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542566.8799888693</v>
+        <v>542606</v>
       </c>
       <c r="R8" t="n">
-        <v>6507081.387940953</v>
+        <v>6507251</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1347,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,15 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105911510</v>
+        <v>97309063</v>
       </c>
       <c r="B9" t="n">
-        <v>57498</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,50 +1390,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>3884</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542593.186904503</v>
+        <v>542504</v>
       </c>
       <c r="R9" t="n">
-        <v>6507198.597062695</v>
+        <v>6507009</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1576,22 +1444,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,15 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105908503</v>
+        <v>131735775</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1634,62 +1487,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205995</v>
+        <v>3884</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Torstorp Väst, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542548.7294210567</v>
+        <v>542493</v>
       </c>
       <c r="R10" t="n">
-        <v>6507074.953257771</v>
+        <v>6506956</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1713,22 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-06-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-06-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1743,27 +1561,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105911649</v>
+        <v>131732483</v>
       </c>
       <c r="B11" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91932</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,50 +1588,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>5445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finspång, Ög</t>
+          <t>Viggestorp Nord, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542579.4901140986</v>
+        <v>542637</v>
       </c>
       <c r="R11" t="n">
-        <v>6507023.324222103</v>
+        <v>6507078</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1838,22 +1642,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,22 +1662,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Amanda Sjölund</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131732483</v>
+        <v>131732490</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>91932</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,14 +1709,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Viggestorp Nord, Ög</t>
+          <t>Torstorp Väst, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542637</v>
+        <v>542473</v>
       </c>
       <c r="R12" t="n">
-        <v>6507078</v>
+        <v>6506985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1984,7 +1782,7 @@
         <v>131736514</v>
       </c>
       <c r="B13" t="n">
-        <v>78675</v>
+        <v>78731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2082,10 +1880,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131733026</v>
+        <v>131736515</v>
       </c>
       <c r="B14" t="n">
-        <v>83294</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,21 +1891,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>311</v>
+        <v>6443</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,10 +1915,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542471</v>
+        <v>542588</v>
       </c>
       <c r="R14" t="n">
-        <v>6507021</v>
+        <v>6507106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,48 +1981,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131732490</v>
+        <v>105908549</v>
       </c>
       <c r="B15" t="n">
-        <v>91850</v>
+        <v>56830</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5445</v>
+        <v>100092</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torstorp Väst, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542473</v>
+        <v>542566</v>
       </c>
       <c r="R15" t="n">
-        <v>6506985</v>
+        <v>6507081</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2248,12 +2067,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-06-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,26 +2087,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131733024</v>
+        <v>105911510</v>
       </c>
       <c r="B16" t="n">
-        <v>83294</v>
+        <v>56830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,37 +2110,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>311</v>
+        <v>100092</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torstorp Väst, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542504</v>
+        <v>542593</v>
       </c>
       <c r="R16" t="n">
-        <v>6506958</v>
+        <v>6507199</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2349,12 +2177,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2369,26 +2197,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131736515</v>
+        <v>105908471</v>
       </c>
       <c r="B17" t="n">
-        <v>78675</v>
+        <v>56823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2396,37 +2220,62 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mäselnleden Sydost, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542588</v>
+        <v>542523</v>
       </c>
       <c r="R17" t="n">
-        <v>6507106</v>
+        <v>6507093</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,12 +2299,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2470,26 +2319,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131733025</v>
+        <v>105908503</v>
       </c>
       <c r="B18" t="n">
-        <v>83294</v>
+        <v>56835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,37 +2342,62 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>311</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torstorp Väst, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542468</v>
+        <v>542549</v>
       </c>
       <c r="R18" t="n">
-        <v>6506932</v>
+        <v>6507075</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,12 +2421,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-06-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-06-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2571,26 +2441,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131735775</v>
+        <v>105911641</v>
       </c>
       <c r="B19" t="n">
-        <v>92480</v>
+        <v>56835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2598,37 +2464,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3884</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Torstorp Väst, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542493</v>
+        <v>542572</v>
       </c>
       <c r="R19" t="n">
-        <v>6506956</v>
+        <v>6507021</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2652,12 +2531,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,64 +2551,85 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131732385</v>
+        <v>105908422</v>
       </c>
       <c r="B20" t="n">
-        <v>96406</v>
+        <v>56816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2671</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Viggestorp Nord, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542607</v>
+        <v>542520</v>
       </c>
       <c r="R20" t="n">
-        <v>6507006</v>
+        <v>6507094</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2753,12 +2653,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2773,26 +2673,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737141</v>
+        <v>105911649</v>
       </c>
       <c r="B21" t="n">
-        <v>75407</v>
+        <v>56816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2800,37 +2696,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1460</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torstorp Väst, Ög</t>
+          <t>Finspång, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542486</v>
+        <v>542579</v>
       </c>
       <c r="R21" t="n">
-        <v>6506934</v>
+        <v>6507023</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2854,12 +2763,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2021-08-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2874,19 +2783,403 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Amanda Sjölund</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>97309055</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>542614</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6507042</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97309061</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>542650</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6507027</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>97309065</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>542664</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6506998</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>97309056</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Finspång, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>542602</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6507114</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Risinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-08-16</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Amanda Sjölund</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55723-2022 artfynd.xlsx
+++ b/artfynd/A 55723-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733024</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733026</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737141</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734436</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309042</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309063</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735775</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732483</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732490</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736514</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736515</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908549</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2206,6 +2281,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911510</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2328,6 +2408,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908471</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2450,6 +2535,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908503</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911641</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2682,6 +2777,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105908422</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105911649</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309055</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2986,6 +3096,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309061</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3083,6 +3198,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309065</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,8 +3300,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97309056</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>